--- a/data/trans_dic/P1404-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P1404-Clase-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>13,77%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>13,48%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>13,63%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,54; 9,11</t>
+          <t>4,37; 9,28</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,62; 12,77</t>
+          <t>6,92; 13,19</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7,7; 13,74</t>
+          <t>7,75; 13,88</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10,64; 16,35</t>
+          <t>11,34; 16,68</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,73; 10,41</t>
+          <t>4,25; 10,34</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,89; 9,83</t>
+          <t>3,67; 9,41</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,17; 11,99</t>
+          <t>5,29; 11,97</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>11,19; 16,19</t>
+          <t>11,03; 16,23</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4,98; 8,76</t>
+          <t>4,98; 8,43</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6,16; 10,48</t>
+          <t>6,22; 10,4</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7,24; 11,79</t>
+          <t>7,22; 11,68</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>11,51; 15,5</t>
+          <t>11,98; 15,59</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>15,98%</t>
+          <t>16,21%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>13,74%</t>
+          <t>13,78%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>5,54; 11,27</t>
+          <t>5,64; 11,39</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6,34; 12,35</t>
+          <t>6,19; 11,98</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7,63; 14,08</t>
+          <t>7,64; 14,47</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13,25; 19,52</t>
+          <t>13,19; 19,65</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,09; 9,14</t>
+          <t>4,09; 9,27</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,76; 10,54</t>
+          <t>4,68; 10,78</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,01; 12,04</t>
+          <t>5,75; 12,08</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>8,89; 13,7</t>
+          <t>8,83; 13,33</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5,43; 9,24</t>
+          <t>5,41; 9,31</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6,33; 10,44</t>
+          <t>6,45; 10,78</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7,56; 12,14</t>
+          <t>7,49; 11,99</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>11,69; 15,87</t>
+          <t>11,89; 15,85</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>17,22%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>20,01%</t>
+          <t>19,45%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>12,98%</t>
+          <t>17,86%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>8,03; 13,16</t>
+          <t>8,02; 13,53</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>11,08; 16,85</t>
+          <t>10,95; 16,74</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>11,21; 17,16</t>
+          <t>11,19; 17,2</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,5; 18,93</t>
+          <t>14,26; 20,61</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5,56; 14,55</t>
+          <t>5,9; 15,21</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,71; 13,01</t>
+          <t>5,57; 13,13</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8,76; 19,88</t>
+          <t>8,38; 21,44</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>15,76; 24,71</t>
+          <t>15,37; 24,4</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>7,97; 12,34</t>
+          <t>8,28; 12,89</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>10,12; 14,66</t>
+          <t>10,14; 14,99</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>11,17; 16,73</t>
+          <t>11,19; 16,62</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>4,79; 19,05</t>
+          <t>15,18; 20,38</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>15,46%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>31,01%</t>
+          <t>12,62%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>23,08%</t>
+          <t>14,23%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>7,55; 10,79</t>
+          <t>7,55; 10,68</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>11,38; 15,41</t>
+          <t>11,46; 15,84</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>10,84; 14,66</t>
+          <t>10,98; 14,71</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>13,43; 17,65</t>
+          <t>13,36; 17,52</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>5,95; 9,76</t>
+          <t>5,68; 9,49</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,16; 11,61</t>
+          <t>7,42; 11,84</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,51; 11,53</t>
+          <t>7,54; 11,66</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>12,26; 64,27</t>
+          <t>10,98; 14,35</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>7,45; 9,85</t>
+          <t>7,3; 9,84</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>10,35; 13,31</t>
+          <t>10,31; 13,36</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>9,84; 12,75</t>
+          <t>9,84; 12,68</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>13,94; 45,15</t>
+          <t>12,84; 15,76</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>16,33%</t>
+          <t>14,85%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>20,39%</t>
+          <t>22,05%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>18,93%</t>
+          <t>19,13%</t>
         </is>
       </c>
     </row>
@@ -1277,69 +1277,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>5,3; 10,65</t>
+          <t>5,34; 10,52</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>10,01; 15,93</t>
+          <t>9,95; 16,12</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10,77; 16,02</t>
+          <t>10,83; 16,03</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>13,53; 19,78</t>
+          <t>12,19; 18,1</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>8,28; 13,91</t>
+          <t>8,52; 13,73</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,1; 20,47</t>
+          <t>14,93; 20,56</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,69; 19,33</t>
+          <t>13,73; 19,26</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>15,08; 23,84</t>
+          <t>19,72; 24,42</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>7,49; 11,52</t>
+          <t>7,67; 11,67</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>13,38; 17,65</t>
+          <t>13,29; 17,71</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>13,11; 17,05</t>
+          <t>12,92; 16,81</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>15,65; 21,45</t>
+          <t>17,33; 21,03</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>18,05%</t>
+          <t>17,74%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>14,33%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,3; 2,72</t>
+          <t>0,3; 2,62</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,35; 4,33</t>
+          <t>0,35; 3,95</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,38; 3,79</t>
+          <t>0,39; 3,89</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,85; 4,88</t>
+          <t>0,81; 4,9</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>11,76; 15,75</t>
+          <t>12,0; 15,94</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>17,25; 22,18</t>
+          <t>16,98; 22,08</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>14,73; 19,77</t>
+          <t>14,83; 19,6</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>16,07; 20,3</t>
+          <t>15,8; 19,94</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>9,75; 13,05</t>
+          <t>9,72; 12,97</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>13,97; 18,13</t>
+          <t>14,14; 18,08</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>11,97; 15,95</t>
+          <t>11,97; 15,91</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>12,6; 16,22</t>
+          <t>12,72; 16,29</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>14,52%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>20,93%</t>
+          <t>16,24%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>15,4%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>7,02; 8,87</t>
+          <t>7,03; 8,92</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>10,28; 12,4</t>
+          <t>10,31; 12,57</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>10,43; 12,58</t>
+          <t>10,49; 12,62</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>10,33; 15,08</t>
+          <t>13,4; 15,63</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>9,29; 11,44</t>
+          <t>9,32; 11,41</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>12,6; 15,08</t>
+          <t>12,58; 15,09</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>12,04; 14,44</t>
+          <t>12,09; 14,44</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>15,72; 37,14</t>
+          <t>15,32; 17,24</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>8,42; 9,91</t>
+          <t>8,48; 9,9</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>11,74; 13,44</t>
+          <t>11,85; 13,48</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>11,56; 13,2</t>
+          <t>11,61; 13,29</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>14,56; 27,1</t>
+          <t>14,69; 16,17</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>67527</t>
+          <t>75808</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>60725</t>
+          <t>65830</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>128252</t>
+          <t>141639</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>21519; 43171</t>
+          <t>20723; 43963</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>28945; 55838</t>
+          <t>30237; 57678</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>33046; 58968</t>
+          <t>33247; 59547</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>53779; 82603</t>
+          <t>62425; 91819</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>14498; 31931</t>
+          <t>13038; 31720</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>12221; 30914</t>
+          <t>11538; 29603</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>17946; 41615</t>
+          <t>18370; 41532</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>50050; 72456</t>
+          <t>53863; 79250</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>38887; 68372</t>
+          <t>38893; 65780</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>46315; 78769</t>
+          <t>46731; 78161</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>56210; 91520</t>
+          <t>56005; 90659</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>109652; 147639</t>
+          <t>124519; 161944</t>
         </is>
       </c>
     </row>
@@ -2082,7 +2082,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>72110</t>
+          <t>78133</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>42301</t>
+          <t>46421</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>114412</t>
+          <t>124553</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>20331; 41354</t>
+          <t>20701; 41806</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>26542; 51735</t>
+          <t>25928; 50187</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>28790; 53118</t>
+          <t>28813; 54603</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>59782; 88038</t>
+          <t>63579; 94748</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>15218; 34004</t>
+          <t>15218; 34463</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>16082; 35630</t>
+          <t>15819; 36450</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>22367; 44839</t>
+          <t>21424; 44988</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>33902; 52234</t>
+          <t>37252; 56234</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>40091; 68264</t>
+          <t>39997; 68807</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>47920; 78997</t>
+          <t>48793; 81606</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>56666; 90991</t>
+          <t>56165; 89832</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>97280; 132104</t>
+          <t>107511; 143323</t>
         </is>
       </c>
     </row>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>74992</t>
+          <t>81085</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>33282</t>
+          <t>36338</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>108273</t>
+          <t>117423</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>43571; 71389</t>
+          <t>43516; 73364</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>69599; 105815</t>
+          <t>68737; 105145</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>58500; 89545</t>
+          <t>58385; 89772</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>30010; 126384</t>
+          <t>67133; 97005</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>9333; 24408</t>
+          <t>9893; 25517</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>14856; 33834</t>
+          <t>14499; 34152</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>14545; 33027</t>
+          <t>13929; 35615</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>26210; 41087</t>
+          <t>28711; 45582</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>56606; 87630</t>
+          <t>58823; 91566</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>89903; 130162</t>
+          <t>90022; 133115</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>76877; 115129</t>
+          <t>76982; 114370</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>39912; 158812</t>
+          <t>99801; 134011</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>160522</t>
+          <t>174357</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>303124</t>
+          <t>108587</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>463646</t>
+          <t>282944</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>93535; 133668</t>
+          <t>93500; 132215</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>131885; 178574</t>
+          <t>132878; 183590</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>124573; 168528</t>
+          <t>126265; 169126</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>138420; 181935</t>
+          <t>150653; 197525</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>42528; 69682</t>
+          <t>40560; 67806</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>54725; 88817</t>
+          <t>56781; 90554</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>62047; 95201</t>
+          <t>62236; 96290</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>119805; 628302</t>
+          <t>94506; 123455</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>145430; 192362</t>
+          <t>142446; 192118</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>199080; 255995</t>
+          <t>198375; 257040</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>194329; 251847</t>
+          <t>194489; 250525</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>279901; 906774</t>
+          <t>255351; 313412</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>77212</t>
+          <t>84004</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>170753</t>
+          <t>182542</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>247966</t>
+          <t>266546</t>
         </is>
       </c>
     </row>
@@ -2759,69 +2759,69 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>18570; 37350</t>
+          <t>18703; 36883</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>51101; 81359</t>
+          <t>50798; 82300</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>66861; 99423</t>
+          <t>67241; 99486</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>63948; 93520</t>
+          <t>68920; 102393</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>47077; 79137</t>
+          <t>48441; 78117</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>114775; 155658</t>
+          <t>113534; 156339</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>101037; 142674</t>
+          <t>101366; 142176</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>126286; 199600</t>
+          <t>163230; 202162</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>68856; 105859</t>
+          <t>70532; 107268</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>170093; 224285</t>
+          <t>168852; 225032</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>178195; 231690</t>
+          <t>175585; 228376</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>205010; 280976</t>
+          <t>241525; 292991</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>5110</t>
+          <t>5157</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>137208</t>
+          <t>149622</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>142318</t>
+          <t>154779</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>909; 8109</t>
+          <t>895; 7810</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>935; 11544</t>
+          <t>932; 10549</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1091; 10891</t>
+          <t>1128; 11171</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2051; 11727</t>
+          <t>1930; 11622</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>146871; 196715</t>
+          <t>149793; 198993</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>191314; 246106</t>
+          <t>188399; 244916</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>159400; 213871</t>
+          <t>160413; 212038</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>122213; 154310</t>
+          <t>133210; 168157</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>150861; 201932</t>
+          <t>150356; 200568</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>192296; 249468</t>
+          <t>194576; 248831</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>163838; 218375</t>
+          <t>163912; 217842</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>126122; 162299</t>
+          <t>137471; 176015</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>457473</t>
+          <t>498544</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>747393</t>
+          <t>589341</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>1204866</t>
+          <t>1087884</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>229426; 290099</t>
+          <t>229992; 291815</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>351597; 424285</t>
+          <t>352485; 429809</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>353144; 425946</t>
+          <t>355260; 427242</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>347790; 507987</t>
+          <t>460242; 536818</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>313868; 386536</t>
+          <t>314819; 385313</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>446738; 534749</t>
+          <t>446326; 535401</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>425322; 509793</t>
+          <t>426805; 510138</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>561405; 1325870</t>
+          <t>556022; 625676</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>559925; 659148</t>
+          <t>563996; 658371</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>817685; 936645</t>
+          <t>825488; 939490</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>799535; 913353</t>
+          <t>803014; 919145</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>1010014; 1880507</t>
+          <t>1037613; 1142126</t>
         </is>
       </c>
     </row>
